--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 05:22:04</t>
+          <t xml:space="preserve">2026-08-05 06:13:17</t>
         </is>
       </c>
     </row>

--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 06:13:17</t>
+          <t xml:space="preserve">2026-08-05 10:03:50</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="49.5" customHeight="1">
+    <row r="84" ht="148.5" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker compose -f &lt;file&gt; build [--no-cache] [service]</t>
+          <t xml:space="preserve">docker compose -f &lt;file&gt; build [--no-cache] [service] を監視プロセス付きで実行 (進捗表示・停滞検知・上限時間での中断。5.7 参照)。開始前に data root の空き容量を確認</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="214.5" customHeight="1">
+    <row r="121" ht="247.5" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -2076,11 +2076,11 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS 未認証、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、ビルド失敗、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗、必須コマンド不足</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="132.0" customHeight="1">
+          <t xml:space="preserve">AWS 未認証、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗、必須コマンド不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="165.0" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、--account-id/--registry 未指定、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、ビルド監視の各値が 0 未満か非数値、--account-id/--registry 未指定、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
@@ -2234,93 +2234,122 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="19.5" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+    <row r="134" ht="82.5" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用。ビルド監視が有効な間は tty を plain へ切り替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="19.5" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《6.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B134" s="8"/>
-    </row>
-    <row r="135" ht="19.5" customHeight="1">
-      <c r="A135" s="3" t="inlineStr">
+      <c r="B135" s="8"/>
+    </row>
+    <row r="136" ht="19.5" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">オプションで指定した値が環境変数より優先されます。</t>
         </is>
       </c>
-      <c r="B135" s="3"/>
-    </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" ht="19.5" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《6.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B136" s="8"/>
-    </row>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="B137" s="8"/>
+    </row>
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="19.5" customHeight="1">
-      <c r="A138" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TZ</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9 に設定し、表示時刻を JST に統一</t>
         </is>
       </c>
     </row>
     <row r="139" ht="19.5" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">TZ</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo または JST-9 に設定し、表示時刻を JST に統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="33.0" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="19.5" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="19.5" customHeight="1">
-      <c r="A140" s="11" t="inlineStr">
+    <row r="142" ht="19.5" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="19.5" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+    <row r="143" ht="19.5" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《6.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B141" s="8"/>
-    </row>
-    <row r="142" ht="19.5" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+      <c r="B143" s="8"/>
+    </row>
+    <row r="144" ht="19.5" customHeight="1">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B142" s="3"/>
+      <c r="B144" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -2362,11 +2391,11 @@
     <mergeCell ref="A124:B124"/>
     <mergeCell ref="A126:B126"/>
     <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A134:B134"/>
     <mergeCell ref="A135:B135"/>
     <mergeCell ref="A136:B136"/>
-    <mergeCell ref="A141:B141"/>
-    <mergeCell ref="A142:B142"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A143:B143"/>
+    <mergeCell ref="A144:B144"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2731,7 +2760,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="33.0" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
@@ -2739,17 +2768,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--container-name NAME</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">任意の文字列</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">--repository の値</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -2759,7 +2788,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json の name</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない (5.7 参照)</t>
         </is>
       </c>
     </row>
@@ -2771,17 +2800,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--output FILE</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -2791,196 +2820,208 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition の出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="33.0" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--dry-run</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (無制限)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33.0" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--no-build-watchdog</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わず、実行内容のみ表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--build-only</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドのみ実行 (build_and_verify.sh へ委譲)。ECR 関連処理は行わない</t>
+          <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--container-name NAME</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">任意の文字列</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--repository の値</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json の name</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33.0" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--output FILE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition の出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--log-dir DIR</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面出力を DIR/build_and_push_&lt;日時&gt;.log にも保存。ディレクトリは自動作成</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--dry-run</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わず、実行内容のみ表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-h, --help</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--build-only</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.4 ビルド前後の一時ファイル</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド前にコピーし、終了後 (成功・失敗を問わず) 自動削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="49.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
-        </is>
-      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ビルドのみ実行 (build_and_verify.sh へ委譲)。ECR 関連処理は行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
+          <t xml:space="preserve">--log-dir DIR</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード文字列</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2991,124 +3032,240 @@
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面出力を DIR/build_and_push_&lt;日時&gt;.log にも保存。ディレクトリは自動作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.4 ビルド前後の一時ファイル</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell PATH</t>
+          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シェルスクリプトのパス</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
-        </is>
-      </c>
-      <c r="E24" s="7"/>
+          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド前にコピーし、終了後 (成功・失敗を問わず) 自動削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="49.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--auto-switchback</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="49.5" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--warn-only</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">既定</t>
+          <t xml:space="preserve">パスワード文字列</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="49.5" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+        </is>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="33.0" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--switchback-shell PATH</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シェルスクリプトのパス</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+        </is>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--auto-switchback</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--warn-only</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定</t>
+        </is>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F26"/>
+  <autoFilter ref="A4:F30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -3358,7 +3515,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="33.0" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
@@ -3366,21 +3523,21 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--container-name NAME</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">--repository の値</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json の name</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない (5.7 参照)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="33.0" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
@@ -3388,180 +3545,261 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--output FILE</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition の出力先</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
     <row r="16" ht="33.0" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell PATH</t>
+          <t xml:space="preserve">--container-name NAME</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+          <t xml:space="preserve">--repository の値</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
+          <t xml:space="preserve">imagedefinition.json の name</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--output FILE</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition の出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33.0" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">4.6 スイッチバック</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--switchback-shell PATH</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--warn-only</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">既定</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="9.0" customHeight="1">
-      <c r="A19" s="0"/>
-    </row>
-    <row r="20" ht="24.0" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="22" ht="9.0" customHeight="1">
+      <c r="A22" s="0"/>
+    </row>
+    <row r="23" ht="24.0" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前提条件</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">権限が無い場合 / 既定は警告して終了 (--warn-only)。--auto-switchback で自動スイッチバック</t>
-        </is>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" ht="33.0" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / 全パラメータの初期値</t>
-        </is>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" ht="49.5" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.4 --copy-file の仕様</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同名ファイル / コピー先に既存ファイルがあると、事故防止のため中止する (exit 1)。ただし --build-only で build_and_verify.sh へ委譲した場合は、委譲先の既定に従い強制上書き (終了時に上書き前のファイルへ復元) となる。委譲時に中止させたい場合は --copy-file-no-overwrite を併用する</t>
-        </is>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" ht="33.0" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
         </is>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
+    <row r="26" ht="33.0" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前半 / 既定値 / 全パラメータの初期値</t>
+        </is>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" ht="49.5" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.4 --copy-file の仕様</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同名ファイル / コピー先に既存ファイルがあると、事故防止のため中止する (exit 1)。ただし --build-only で build_and_verify.sh へ委譲した場合は、委譲先の既定に従い強制上書き (終了時に上書き前のファイルへ復元) となる。委譲時に中止させたい場合は --copy-file-no-overwrite を併用する</t>
+        </is>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" ht="33.0" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
+        </is>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" ht="33.0" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
+        </is>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3774,7 +4012,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="82.5" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -3782,12 +4020,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">レジストリを直接指定 (アカウント ID 不要)</t>
+          <t xml:space="preserve">レジストリを直接指定 (アカウント ID 不要)
+ビルドが exporting layers から進まないときの調査 (進捗 10 秒 / 停滞判定 60 秒)
+30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">./build_and_push.sh --registry 123456789012.dkr.ecr.ap-northeast-1.amazonaws.com</t>
+          <t xml:space="preserve">./build_and_push.sh --registry 123456789012.dkr.ecr.ap-northeast-1.amazonaws.com
+./build_and_push.sh --account-id 123456789012 \
+    --build-progress-interval 10 --build-stall-timeout 60
+./build_and_push.sh --account-id 123456789012 --build-timeout 1800</t>
         </is>
       </c>
     </row>

--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 10:03:50</t>
+          <t xml:space="preserve">2026-08-11 15:06:08</t>
         </is>
       </c>
     </row>

--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11 15:06:08</t>
+          <t xml:space="preserve">2026-08-12 13:21:32</t>
         </is>
       </c>
     </row>
@@ -2234,122 +2234,151 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="82.5" customHeight="1">
+    <row r="134" ht="66.0" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle-env</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">事前 export 済みなら、その tar のパスをそのまま使用 (--cacert-dir 未指定時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="82.5" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用。ビルド監視が有効な間は tty を plain へ切り替える</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="19.5" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="136" ht="19.5" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《6.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B135" s="8"/>
-    </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="B136" s="8"/>
+    </row>
+    <row r="137" ht="19.5" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">オプションで指定した値が環境変数より優先されます。</t>
         </is>
       </c>
-      <c r="B136" s="3"/>
-    </row>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《6.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B137" s="8"/>
-    </row>
-    <row r="138" ht="19.5" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="B138" s="8"/>
+    </row>
+    <row r="139" ht="19.5" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="19.5" customHeight="1">
-      <c r="A139" s="11" t="inlineStr">
+    <row r="140" ht="19.5" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">TZ</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia/Tokyo または JST-9 に設定し、表示時刻を JST に統一</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="33.0" customHeight="1">
-      <c r="A140" s="11" t="inlineStr">
+    <row r="141" ht="33.0" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="19.5" customHeight="1">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
         </is>
       </c>
     </row>
     <row r="142" ht="19.5" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="19.5" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="19.5" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="144" ht="33.0" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CA 証明書をまとめた tar のパス。compose の file 型シークレットへ渡す。--cacert-dir 未指定時は「空の tar」のパスが入り、従来どおり証明書なしでビルドされる</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="19.5" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《6.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B143" s="8"/>
-    </row>
-    <row r="144" ht="19.5" customHeight="1">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="B145" s="8"/>
+    </row>
+    <row r="146" ht="19.5" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B144" s="3"/>
+      <c r="B146" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -2391,11 +2420,11 @@
     <mergeCell ref="A124:B124"/>
     <mergeCell ref="A126:B126"/>
     <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A135:B135"/>
     <mergeCell ref="A136:B136"/>
     <mergeCell ref="A137:B137"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="A144:B144"/>
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="A146:B146"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3264,8 +3293,156 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="33.0" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-dir DIR</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリのパス</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33.0" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英数字と . _ -</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
+        </is>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名、Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33.0" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパス</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時ファイル</t>
+        </is>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+        </is>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33.0" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">glob パターン</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F30"/>
+  <autoFilter ref="A4:F35"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -3691,115 +3868,218 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="9.0" customHeight="1">
-      <c r="A22" s="0"/>
-    </row>
-    <row r="23" ht="24.0" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="22" ht="33.0" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名、Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33.0" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時ファイル</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="33.0" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33.0" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="9.0" customHeight="1">
+      <c r="A26" s="0"/>
+    </row>
+    <row r="27" ht="24.0" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前提条件</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">権限が無い場合 / 既定は警告して終了 (--warn-only)。--auto-switchback で自動スイッチバック</t>
-        </is>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" ht="33.0" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / 全パラメータの初期値</t>
-        </is>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" ht="49.5" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.4 --copy-file の仕様</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同名ファイル / コピー先に既存ファイルがあると、事故防止のため中止する (exit 1)。ただし --build-only で build_and_verify.sh へ委譲した場合は、委譲先の既定に従い強制上書き (終了時に上書き前のファイルへ復元) となる。委譲時に中止させたい場合は --copy-file-no-overwrite を併用する</t>
-        </is>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" ht="33.0" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
-        </is>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" ht="33.0" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2 スクリプトが設定する環境変数</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
         </is>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
+    <row r="30" ht="33.0" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1 ファイル内のセクション構成</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前半 / 既定値 / 全パラメータの初期値</t>
+        </is>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" ht="49.5" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.4 --copy-file の仕様</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同名ファイル / コピー先に既存ファイルがあると、事故防止のため中止する (exit 1)。ただし --build-only で build_and_verify.sh へ委譲した場合は、委譲先の既定に従い強制上書き (終了時に上書き前のファイルへ復元) となる。委譲時に中止させたい場合は --copy-file-no-overwrite を併用する</t>
+        </is>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" ht="33.0" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
+        </is>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" ht="33.0" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-bundle-env / 事前 export 済みなら、その tar のパスをそのまま使用 (--cacert-dir 未指定時)</t>
+        </is>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
+        </is>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12 13:21:32</t>
+          <t xml:space="preserve">2026-08-13 16:17:49</t>
         </is>
       </c>
     </row>

--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-13 16:17:49</t>
+          <t xml:space="preserve">2026-08-14 20:41:49</t>
         </is>
       </c>
     </row>

--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-14 20:41:49</t>
+          <t xml:space="preserve">2026-08-22 04:58:59</t>
         </is>
       </c>
     </row>

--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-22 04:58:59</t>
+          <t xml:space="preserve">2026-08-29 22:04:17</t>
         </is>
       </c>
     </row>
